--- a/評価シート改訂案/改訂案B_点数改良版.xlsx
+++ b/評価シート改訂案/改訂案B_点数改良版.xlsx
@@ -118,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -140,11 +140,128 @@
         <color rgb="00A6A6A6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +327,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -589,7 +715,7 @@
           <t>評価シート改訂案 B【点数改良版（現行踏襲）】　― 改訂のポイント ―</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="23" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
@@ -597,7 +723,7 @@
           <t>■ 現行シートの問題と、この案での対応</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -619,7 +745,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>全項目に「期待水準（A）の定義」と着眼点を明記。S・B以下を付ける場合は「根拠となる事実」の記入を必須にした</t>
+          <t>全項目に着眼点と採点基準（10・7・4・0点の意味）を明記。10点・4点・0点を付ける場合は「根拠となる事実」の記入を必須にした</t>
         </is>
       </c>
     </row>
@@ -631,7 +757,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>「A（期待どおり）＝標準の良い評価」「Sは期待超えの事実がある場合」と定義。満点かどうかではなく基準に対する事実で説明できる</t>
+          <t>「7点＝期待どおり＝標準」「10点は期待超えの事実がある場合」と定義。満点かどうかではなく基準に対する事実で説明できる</t>
         </is>
       </c>
     </row>
@@ -689,7 +815,7 @@
           <t>■ この案の仕組み</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="23" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
@@ -697,7 +823,7 @@
           <t>・現行の100点満点・合計点→S〜D換算（S:91〜100／A:71〜90／B:51〜70／C:41〜50／D:40以下）はそのまま維持。給与・号数への接続も現行どおり</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="23" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -705,7 +831,7 @@
           <t>・「1点×5項目の1 or 0チェック」を廃止し、各項目を10・7・4・0点の4段階に変更（7点＝期待どおり、が標準）。「なぜ満点じゃないのか」→「10点は期待超えの事実がある場合」と説明できる</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="23" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
@@ -713,7 +839,7 @@
           <t>・配点構成を3部署とも 成果50点・能力30点・姿勢20点 に統一（現行は営業だけ成果65点で、目標未達時に部署間の点差が大きく開く原因だった）</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
+      <c r="C16" s="23" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
@@ -721,7 +847,7 @@
           <t>・採点する行を約30行→8行に削減。旧シートの細かい設問は「着眼点」として項目内に残したので、見るポイントは変わらない</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="23" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
@@ -729,47 +855,47 @@
           <t>・コメント欄は「根拠となる事実」欄に一本化し、月次ログからの転記で書けるようにした</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>■ 運用ルール（シートよりも大事な4つ）</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
+          <t>■ 運用ルール</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>① A（期待どおり）が標準。全項目Aは「問題なくできている良い評価」であることを全員に説明する</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n"/>
+          <t>① 7点（期待どおり）が標準。全項目7点は「問題なくできている良い評価」</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>② S・B・C・Dを付けるときは「根拠となる事実」を必ず記入する（書けない場合はAに戻す）</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n"/>
+          <t>② 10点・4点・0点を付けるときは「根拠となる事実」を記入する（月報から転記でOK）</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>③ 評価者同士で「目線合わせ会議」を評価前に30分行う（同じ事実に同じ評価が付くように）</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n"/>
+          <t>③ 合計点と総合評価はExcelが自動計算する（S〜Dへの換算は現行どおり）</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>④ 評価は必ず本人へのフィードバック面談（10〜15分）で説明する。月次ログがあれば話す材料に困らない</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n"/>
+          <t>④ 最終評価と昇給幅は、これまでどおり社長が決定する</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -819,14 +945,14 @@
           <t>人事評価シート【点数改良版】　電算・編集</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="23" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -881,17 +1007,17 @@
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="23" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="23" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -899,14 +1025,14 @@
           <t>使い方：①業務目標達成度は換算表どおりに点を付ける。それ以外は 10・7・4・0 の4段階（7点＝期待どおり＝標準）。10点・4点・0点を付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -990,7 +1116,7 @@
       <c r="I9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="25" t="n"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
           <t>課題目標（部署）</t>
@@ -1018,7 +1144,7 @@
       <c r="I10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="26" t="n"/>
       <c r="B11" s="12" t="inlineStr">
         <is>
           <t>課題目標（個人）</t>
@@ -1079,7 +1205,7 @@
       <c r="I12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="25" t="n"/>
       <c r="B13" s="12" t="inlineStr">
         <is>
           <t>実行力・正確性</t>
@@ -1107,7 +1233,7 @@
       <c r="I13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="26" t="n"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
           <t>改善・再発防止</t>
@@ -1168,7 +1294,7 @@
       <c r="I15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="n"/>
+      <c r="A16" s="26" t="n"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>協調性・報連相</t>
@@ -1233,12 +1359,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）</t>
+          <t>最終総合評価（社長が決定）</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
@@ -1246,36 +1372,36 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="23" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="27" t="n"/>
+      <c r="I22" s="28" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="n"/>
+      <c r="I23" s="31" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
@@ -1283,36 +1409,36 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="23" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="16" t="inlineStr"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="28" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="30" t="n"/>
+      <c r="I26" s="31" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="6" t="inlineStr">
@@ -1393,14 +1519,14 @@
           <t>人事評価シート【点数改良版】　営業</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="23" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1455,17 +1581,17 @@
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="23" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="23" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -1473,14 +1599,14 @@
           <t>使い方：①業務目標達成度は換算表どおりに点を付ける。それ以外は 10・7・4・0 の4段階（7点＝期待どおり＝標準）。10点・4点・0点を付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1564,7 +1690,7 @@
       <c r="I9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="25" t="n"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
           <t>課題目標（部署）</t>
@@ -1592,7 +1718,7 @@
       <c r="I10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="26" t="n"/>
       <c r="B11" s="12" t="inlineStr">
         <is>
           <t>課題目標（個人）</t>
@@ -1653,7 +1779,7 @@
       <c r="I12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="25" t="n"/>
       <c r="B13" s="12" t="inlineStr">
         <is>
           <t>実行力・正確性</t>
@@ -1681,7 +1807,7 @@
       <c r="I13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="26" t="n"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
           <t>改善・再発防止</t>
@@ -1742,7 +1868,7 @@
       <c r="I15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="n"/>
+      <c r="A16" s="26" t="n"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>協調性・報連相</t>
@@ -1807,12 +1933,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）</t>
+          <t>最終総合評価（社長が決定）</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
@@ -1820,36 +1946,36 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="23" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="27" t="n"/>
+      <c r="I22" s="28" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="n"/>
+      <c r="I23" s="31" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
@@ -1857,36 +1983,36 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="23" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="16" t="inlineStr"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="28" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="30" t="n"/>
+      <c r="I26" s="31" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="6" t="inlineStr">
@@ -1967,14 +2093,14 @@
           <t>人事評価シート【点数改良版】　工場</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="23" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2029,17 +2155,17 @@
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="23" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="23" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -2047,14 +2173,14 @@
           <t>使い方：①業務目標達成度は換算表どおりに点を付ける。それ以外は 10・7・4・0 の4段階（7点＝期待どおり＝標準）。10点・4点・0点を付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -2138,7 +2264,7 @@
       <c r="I9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="25" t="n"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
           <t>課題目標（部署）</t>
@@ -2166,7 +2292,7 @@
       <c r="I10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="26" t="n"/>
       <c r="B11" s="12" t="inlineStr">
         <is>
           <t>課題目標（個人）</t>
@@ -2227,7 +2353,7 @@
       <c r="I12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="25" t="n"/>
       <c r="B13" s="12" t="inlineStr">
         <is>
           <t>実行力・正確性</t>
@@ -2255,7 +2381,7 @@
       <c r="I13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="26" t="n"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
           <t>改善・再発防止</t>
@@ -2316,7 +2442,7 @@
       <c r="I15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="n"/>
+      <c r="A16" s="26" t="n"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>協調性・報連相</t>
@@ -2381,12 +2507,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）</t>
+          <t>最終総合評価（社長が決定）</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
@@ -2394,36 +2520,36 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="23" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="27" t="n"/>
+      <c r="I22" s="28" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="n"/>
+      <c r="I23" s="31" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
@@ -2431,36 +2557,36 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="23" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="16" t="inlineStr"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="28" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="30" t="n"/>
+      <c r="I26" s="31" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="6" t="inlineStr">
@@ -2537,9 +2663,9 @@
           <t>日々の記録（月次ログ）　― 月末に5分、1行ずつでOK ―</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="23" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="B3" s="9" t="inlineStr">
@@ -2547,9 +2673,9 @@
           <t>使い方：月末に「良かったこと・成果」「課題・反省」を1行ずつ書くだけ。上司も気づいたことがあれば一言。期末の評価シートの「根拠となる事実」「本人コメント」は、ここから転記すれば書けます（記憶に頼らない・直近だけで評価しないための仕組み）。</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="10" t="inlineStr">
